--- a/output/pdf_financials_xlsx/RFR.xlsx
+++ b/output/pdf_financials_xlsx/RFR.xlsx
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>4.97888</v>
+        <v>5.264943</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>5.179543</v>
+        <v>5.349954</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>5.409574</v>
+        <v>5.733965</v>
       </c>
     </row>
     <row r="93">
@@ -2999,7 +2999,11 @@
           <t>Warrant reserve (note 7 (c))</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3255,7 +3259,11 @@
           <t>Warrant reserve (note 8 (c))</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>0.286063</v>
       </c>

--- a/output/pdf_financials_xlsx/RFR.xlsx
+++ b/output/pdf_financials_xlsx/RFR.xlsx
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.356578</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.201309</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.404883</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.356578</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.201309</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.404883</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.660197</v>
+        <v>0.303619</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.313402</v>
+        <v>0.112093</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.474473</v>
+        <v>0.06959</v>
       </c>
     </row>
     <row r="49">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/RFR.xlsx
+++ b/output/pdf_financials_xlsx/RFR.xlsx
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>1.697209</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -3995,7 +3995,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="n">
         <v>1.697209</v>
       </c>
